--- a/smart phone dataset.xlsx
+++ b/smart phone dataset.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/43cff1c8262fe832/Masaüstü/Project Study/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Selen\Documents\Distance-Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{D985AE7B-6A36-41D1-AA85-7ED59463C360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{196A61BA-5546-46E9-8002-4FEBF89969E0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B90AB7-C10C-4090-A0C3-1203F2BDC7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{4461C1B7-D170-B646-A3E3-4EBC5C75C788}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4461C1B7-D170-B646-A3E3-4EBC5C75C788}"/>
   </bookViews>
   <sheets>
     <sheet name="Edited" sheetId="1" r:id="rId1"/>
@@ -8794,6 +8794,7 @@
   <dimension ref="A1:K1021"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
+    <col min="1" max="1" width="46.8984375" customWidth="1"/>
     <col min="8" max="8" width="54.69921875" customWidth="1"/>
   </cols>
   <sheetData>

--- a/smart phone dataset.xlsx
+++ b/smart phone dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Selen\Documents\Distance-Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B90AB7-C10C-4090-A0C3-1203F2BDC7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAAFEFA-52DE-4EFE-B076-4C3C3917E35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4461C1B7-D170-B646-A3E3-4EBC5C75C788}"/>
   </bookViews>
@@ -8390,7 +8390,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -8424,6 +8424,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -8451,17 +8458,253 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -8472,6 +8715,26 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AD4C8361-6B0B-4669-827D-CEDC69500106}" name="Table1" displayName="Table1" ref="A1:K1021" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:K1021" xr:uid="{AD4C8361-6B0B-4669-827D-CEDC69500106}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{C9926F9F-8E04-4FA4-B127-0EC1898C20B0}" name="model" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{C119AA49-3E8B-4B7F-AB5D-C14D47A13E67}" name="price" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{D049E59D-21F4-40FC-8DC8-AADDF4FEA918}" name="rating" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{6D6B41D9-AE53-45C6-BDB5-68B9DBF8BAEB}" name="sim" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{DB3AD9ED-65E0-4ED7-9723-AF4BE6349743}" name="processor" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{6D7EAE07-4419-4309-8660-53B996216E8C}" name="ram" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{1B274F27-4576-44F4-B563-57AE2F51BB55}" name="battery" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{08EC735E-52B0-4FA4-82E0-90D29DD3A9DA}" name="display" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{6090D356-0D22-44F5-B753-3048D7A20A75}" name="camera" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{9E75DDD2-ECDC-4F5F-8677-C980749318AE}" name="card" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{27718F08-FE27-4A98-BDD5-3633304B0BC8}" name="os" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8799,37 +9062,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -44202,8 +44465,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{3FE8D042-7D0F-814E-B6D3-C7515EA14A0B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
